--- a/balance/weapons.xlsx
+++ b/balance/weapons.xlsx
@@ -1286,7 +1286,7 @@
         <v>47</v>
       </c>
       <c r="E9" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -1320,7 +1320,7 @@
         <v>51</v>
       </c>
       <c r="E10" s="8">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -1330,13 +1330,13 @@
         <v>350</v>
       </c>
       <c r="K10" s="8">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L10" s="8">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="M10" s="8">
-        <v>3.2</v>
+        <v>0.65</v>
       </c>
       <c r="N10" s="8">
         <v>6</v>
@@ -1372,13 +1372,13 @@
         <v>400</v>
       </c>
       <c r="K11" s="8">
-        <v>1400</v>
+        <v>850</v>
       </c>
       <c r="L11" s="8">
-        <v>650</v>
+        <v>300</v>
       </c>
       <c r="M11" s="8">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="N11" s="8">
         <v>6</v>
@@ -1402,7 +1402,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
